--- a/excel_template/Easyrewardz_Live.xlsx
+++ b/excel_template/Easyrewardz_Live.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -597,27 +597,26 @@
       <c r="B10" s="3" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>The 'Company Info' sheet (optional)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>A second sheet with plain Field | Value rows — no header row, no formulas. Every field is optional: the dashboard only renders what you fill in, and hides the whole Business Description section if the sheet isn't present at all. Supported fields — 'Company Name'; 'Business Description' (one paragraph); 'Tag 1' through 'Tag 4' (short capability tags shown as chips); 'Scale Metric 1/2/3 Label' and the matching '...Value' (e.g. Label='Brands', Value='220+'); and 'Strategic Note Label' / 'Strategic Note Value' / 'Strategic Note Sub' (a one-off callout, e.g. a recent product launch). See the pre-filled 'Company Info' sheet in this workbook for a worked example.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Key Performance Indicators table (Platform / SetUp / Campaign Management)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>The dashboard's "Key Performance Indicators" table looks for three revenue-mix KPIs — Platform Revenue, SetUp Revenue, Campaign Management — as a % of Total Revenue. It does NOT require those exact row names: it searches Monthly Data's revenue rows for common synonyms (Platform Revenue matches rows containing "platform", "software revenue", "SaaS revenue", "technology revenue", or "subscription"; SetUp Revenue matches "setup"/"set-up", "onboarding", "deployment", "implementation", or "integration revenue"; Campaign Management matches "campaign"). Add a row named accordingly if you track that revenue separately, and it populates automatically on next upload — no code change needed. If your sheet has no row matching a concept, that KPI shows N/A rather than guessing, since collapsing an unrelated revenue line into the wrong KPI would misstate it.</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>This is Easyrewardz's live dashboard file</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>This workbook holds Easyrewardz's real financials (Monthly Data), real company profile (Company Info), and real, sourced News Feed / Industry Data — it's the one to upload day-to-day for this company's dashboard. The News Feed and Industry Data sheets are refreshed automatically once a day by a scheduled research job when this file is reachable; Monthly Data and Company Info are updated manually as usual. To set up a DIFFERENT company's dashboard, start from excel_template/Mastersheet_Template.xlsx instead — that copy is kept generic/blank so it never carries Easyrewardz-specific data forward.</t>
+          <t>The 'Company Info' sheet (optional)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>A second sheet with plain Field | Value rows — no header row, no formulas. Every field is optional: the dashboard only renders what you fill in, and hides the whole Business Description section if the sheet isn't present at all. Supported fields — 'Company Name'; 'Business Description' (one paragraph); 'Tag 1' through 'Tag 4' (short capability tags shown as chips); 'Scale Metric 1/2/3 Label' and the matching '...Value' (e.g. Label='Brands', Value='220+'); and 'Strategic Note Label' / 'Strategic Note Value' / 'Strategic Note Sub' (a one-off callout, e.g. a recent product launch). See the pre-filled 'Company Info' sheet in this workbook for a worked example.</t>
         </is>
       </c>
     </row>
@@ -625,12 +624,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Current data range (this copy)</t>
+          <t>This is Easyrewardz's live dashboard file</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Monthly Data: 2021-03 through 2026-06 (64 months) of Easyrewardz's real historical financials. News Feed / Industry Data: see the Data Refresh sheet for when each was last verified.</t>
+          <t>This workbook holds Easyrewardz's real financials (Monthly Data), real company profile (Company Info), and real, sourced News Feed / Industry Data — it's the one to upload day-to-day for this company's dashboard. The News Feed and Industry Data sheets are refreshed automatically once a day by a scheduled research job when this file is reachable; Monthly Data and Company Info are updated manually as usual. To set up a DIFFERENT company's dashboard, start from excel_template/Mastersheet_Template.xlsx instead — that copy is kept generic/blank so it never carries Easyrewardz-specific data forward.</t>
         </is>
       </c>
     </row>
@@ -638,10 +637,23 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>Current data range (this copy)</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Monthly Data: 2021-03 through 2026-06 (64 months) of Easyrewardz's real historical financials. News Feed / Industry Data: see the Data Refresh sheet for when each was last verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>The 'News Feed' and 'Industry Data' sheets (optional, Phase 2)</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Two more optional sheets power the News &amp; Updates and Industry &amp; Competitors sections. 'News Feed' is one row per news item (Title, Summary, Category, Published Date, Source Name, Source URL, Source Tier, Secondary Source Name/URL, Tags). 'Industry Data' is a long/tidy Section | Item | Field | Value table covering the industry overview, snapshot metrics, trends, competitor comparison and dashboard analysis. Both are populated by an independent research pipeline, refreshed on a schedule, and kept separate from the financial 'Monthly Data' pipeline — a missing or malformed sheet here never affects the Performance section. An optional 'Data Refresh' sheet (two Field | Value rows) records when each was last updated.</t>
         </is>
@@ -844,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM11"/>
+  <dimension ref="A1:BM13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1910,1172 +1922,1186 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Direct Expenses</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="n">
-        <v>9013959.93</v>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>7968438.1</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>6267835.640000001</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>8578898.789999999</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>11448686.65</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>11482975.88</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>9720394.306</v>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>11239511.93</v>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v>10962776.61</v>
-      </c>
-      <c r="K6" s="10" t="n">
-        <v>11604476.28</v>
-      </c>
-      <c r="L6" s="10" t="n">
-        <v>12210785.55</v>
-      </c>
-      <c r="M6" s="10" t="n">
-        <v>10392528.57</v>
-      </c>
-      <c r="N6" s="10" t="n">
-        <v>12296567.31</v>
-      </c>
-      <c r="O6" s="10" t="n">
-        <v>10611347.57</v>
-      </c>
-      <c r="P6" s="10" t="n">
-        <v>11956035.3</v>
-      </c>
-      <c r="Q6" s="10" t="n">
-        <v>13774906.51</v>
-      </c>
-      <c r="R6" s="10" t="n">
-        <v>14311708.45</v>
-      </c>
-      <c r="S6" s="10" t="n">
-        <v>15107825.25</v>
-      </c>
-      <c r="T6" s="10" t="n">
-        <v>15073778.41</v>
-      </c>
-      <c r="U6" s="10" t="n">
-        <v>14418592.17</v>
-      </c>
-      <c r="V6" s="10" t="n">
-        <v>14254171.786</v>
-      </c>
-      <c r="W6" s="10" t="n">
-        <v>12876882.05</v>
-      </c>
-      <c r="X6" s="10" t="n">
-        <v>14611496.09</v>
-      </c>
-      <c r="Y6" s="10" t="n">
-        <v>12166751.06</v>
-      </c>
-      <c r="Z6" s="10" t="n">
-        <v>16621576.62</v>
-      </c>
-      <c r="AA6" s="10" t="n">
-        <v>14514309.01576271</v>
-      </c>
-      <c r="AB6" s="10" t="n">
-        <v>14531796.8503</v>
-      </c>
-      <c r="AC6" s="10" t="n">
-        <v>17101692.03703327</v>
-      </c>
-      <c r="AD6" s="10" t="n">
-        <v>14931033.79</v>
-      </c>
-      <c r="AE6" s="10" t="n">
-        <v>16808491.76</v>
-      </c>
-      <c r="AF6" s="10" t="n">
-        <v>16843990.58</v>
-      </c>
-      <c r="AG6" s="10" t="n">
-        <v>21912897.99750356</v>
-      </c>
-      <c r="AH6" s="10" t="n">
-        <v>19061337.28443</v>
-      </c>
-      <c r="AI6" s="10" t="n">
-        <v>21717989.15</v>
-      </c>
-      <c r="AJ6" s="10" t="n">
-        <v>21221983.031</v>
-      </c>
-      <c r="AK6" s="10" t="n">
-        <v>19401999.32</v>
-      </c>
-      <c r="AL6" s="10" t="n">
-        <v>20302133.71</v>
-      </c>
-      <c r="AM6" s="10" t="n">
-        <v>19376025.52</v>
-      </c>
-      <c r="AN6" s="10" t="n">
-        <v>20068914.47</v>
-      </c>
-      <c r="AO6" s="10" t="n">
-        <v>22682071.0394</v>
-      </c>
-      <c r="AP6" s="10" t="n">
-        <v>20373300.64776801</v>
-      </c>
-      <c r="AQ6" s="10" t="n">
-        <v>19367394.8239</v>
-      </c>
-      <c r="AR6" s="10" t="n">
-        <v>18011637.16812</v>
-      </c>
-      <c r="AS6" s="10" t="n">
-        <v>20063869.77305</v>
-      </c>
-      <c r="AT6" s="10" t="n">
-        <v>18945057.16586</v>
-      </c>
-      <c r="AU6" s="10" t="n">
-        <v>21338655.664084</v>
-      </c>
-      <c r="AV6" s="10" t="n">
-        <v>21431476.52</v>
-      </c>
-      <c r="AW6" s="10" t="n">
-        <v>21198056.54</v>
-      </c>
-      <c r="AX6" s="10" t="n">
-        <v>23400701.64</v>
-      </c>
-      <c r="AY6" s="10" t="n">
-        <v>19755778.5</v>
-      </c>
-      <c r="AZ6" s="10" t="n">
-        <v>20926547.08</v>
-      </c>
-      <c r="BA6" s="10" t="n">
-        <v>22438247.56</v>
-      </c>
-      <c r="BB6" s="10" t="n">
-        <v>23520051.4</v>
-      </c>
-      <c r="BC6" s="10" t="n">
-        <v>23108741.32</v>
-      </c>
-      <c r="BD6" s="10" t="n">
-        <v>24842686.74</v>
-      </c>
-      <c r="BE6" s="10" t="n">
-        <v>31015231.63</v>
-      </c>
-      <c r="BF6" s="10" t="n">
-        <v>37452085.42</v>
-      </c>
-      <c r="BG6" s="10" t="n">
-        <v>40054821.34915254</v>
-      </c>
-      <c r="BH6" s="10" t="n">
-        <v>37864126</v>
-      </c>
-      <c r="BI6" s="10" t="n">
-        <v>39769304</v>
-      </c>
-      <c r="BJ6" s="10" t="n">
-        <v>38179519</v>
-      </c>
-      <c r="BK6" s="10" t="n">
-        <v>31309508</v>
-      </c>
-      <c r="BL6" s="10" t="n">
-        <v>39291548.26695399</v>
-      </c>
-      <c r="BM6" s="10" t="n">
-        <v>29792746.75</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Platform Revenue</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="n">
-        <v>27674794.07</v>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>14079792.69898305</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>14707620.8335</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>13352982.21</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>17665215.8235</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>17883955.78726923</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>27521875.0168814</v>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>15928646.49559324</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>17563977.50750002</v>
-      </c>
-      <c r="K7" s="10" t="n">
-        <v>16669674.72</v>
-      </c>
-      <c r="L7" s="10" t="n">
-        <v>18845739.543</v>
-      </c>
-      <c r="M7" s="10" t="n">
-        <v>18673566.68</v>
-      </c>
-      <c r="N7" s="10" t="n">
-        <v>35834343.60130242</v>
-      </c>
-      <c r="O7" s="10" t="n">
-        <v>17106390.7138983</v>
-      </c>
-      <c r="P7" s="10" t="n">
-        <v>15263138.93102542</v>
-      </c>
-      <c r="Q7" s="10" t="n">
-        <v>17636726.36823913</v>
-      </c>
-      <c r="R7" s="10" t="n">
-        <v>20289752.1245</v>
-      </c>
-      <c r="S7" s="10" t="n">
-        <v>17388271.28381356</v>
-      </c>
-      <c r="T7" s="10" t="n">
-        <v>22683385.89</v>
-      </c>
-      <c r="U7" s="10" t="n">
-        <v>22403658.23</v>
-      </c>
-      <c r="V7" s="10" t="n">
-        <v>23025259.834</v>
-      </c>
-      <c r="W7" s="10" t="n">
-        <v>28464918.03</v>
-      </c>
-      <c r="X7" s="10" t="n">
-        <v>28910476.67</v>
-      </c>
-      <c r="Y7" s="10" t="n">
-        <v>29156049.89</v>
-      </c>
-      <c r="Z7" s="10" t="n">
-        <v>32737497.57999999</v>
-      </c>
-      <c r="AA7" s="10" t="n">
-        <v>30612227.85423729</v>
-      </c>
-      <c r="AB7" s="10" t="n">
-        <v>27241349.96963943</v>
-      </c>
-      <c r="AC7" s="10" t="n">
-        <v>32930990.19896673</v>
-      </c>
-      <c r="AD7" s="10" t="n">
-        <v>33434436.21</v>
-      </c>
-      <c r="AE7" s="10" t="n">
-        <v>34709799.0652</v>
-      </c>
-      <c r="AF7" s="10" t="n">
-        <v>35593982.1624</v>
-      </c>
-      <c r="AG7" s="10" t="n">
-        <v>34718689.51430025</v>
-      </c>
-      <c r="AH7" s="10" t="n">
-        <v>39946311.25570561</v>
-      </c>
-      <c r="AI7" s="10" t="n">
-        <v>44543684.85</v>
-      </c>
-      <c r="AJ7" s="10" t="n">
-        <v>44753436.969</v>
-      </c>
-      <c r="AK7" s="10" t="n">
-        <v>43836805.68</v>
-      </c>
-      <c r="AL7" s="10" t="n">
-        <v>47142261.9175</v>
-      </c>
-      <c r="AM7" s="10" t="n">
-        <v>43405622.98822826</v>
-      </c>
-      <c r="AN7" s="10" t="n">
-        <v>40845517.03634186</v>
-      </c>
-      <c r="AO7" s="10" t="n">
-        <v>42404588.65137531</v>
-      </c>
-      <c r="AP7" s="10" t="n">
-        <v>43170391.11173046</v>
-      </c>
-      <c r="AQ7" s="10" t="n">
-        <v>40543523.4387265</v>
-      </c>
-      <c r="AR7" s="10" t="n">
-        <v>41864482.4902292</v>
-      </c>
-      <c r="AS7" s="10" t="n">
-        <v>42362383.16435</v>
-      </c>
-      <c r="AT7" s="10" t="n">
-        <v>41520227.54187846</v>
-      </c>
-      <c r="AU7" s="10" t="n">
-        <v>41888931.335916</v>
-      </c>
-      <c r="AV7" s="10" t="n">
-        <v>41433600.97308891</v>
-      </c>
-      <c r="AW7" s="10" t="n">
-        <v>42165257.92661601</v>
-      </c>
-      <c r="AX7" s="10" t="n">
-        <v>44680347.68243356</v>
-      </c>
-      <c r="AY7" s="10" t="n">
-        <v>43376942.7241476</v>
-      </c>
-      <c r="AZ7" s="10" t="n">
-        <v>43667582.8847267</v>
-      </c>
-      <c r="BA7" s="10" t="n">
-        <v>44820065.842832</v>
-      </c>
-      <c r="BB7" s="10" t="n">
-        <v>45510015.96067599</v>
-      </c>
-      <c r="BC7" s="10" t="n">
-        <v>43682598.93386099</v>
-      </c>
-      <c r="BD7" s="10" t="n">
-        <v>43697365.80847485</v>
-      </c>
-      <c r="BE7" s="10" t="n">
-        <v>42352202.37</v>
-      </c>
-      <c r="BF7" s="10" t="n">
-        <v>42454030.67803611</v>
-      </c>
-      <c r="BG7" s="10" t="n">
-        <v>42213091.15237298</v>
-      </c>
-      <c r="BH7" s="10" t="n">
-        <v>41046838.7629897</v>
-      </c>
-      <c r="BI7" s="10" t="n">
-        <v>41390968.56394804</v>
-      </c>
-      <c r="BJ7" s="10" t="n">
-        <v>41452901.79445086</v>
-      </c>
-      <c r="BK7" s="10" t="n">
-        <v>41214185.46080001</v>
-      </c>
-      <c r="BL7" s="10" t="n">
-        <v>44412362.26497991</v>
-      </c>
-      <c r="BM7" s="10" t="n">
-        <v>45459370.535</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SetUp Revenue</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Indirect Expenses</t>
+          <t>Direct Expenses</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>32353126.38</v>
+        <v>9013959.93</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>25154469.64</v>
+        <v>7968438.1</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>27096984.62</v>
+        <v>6267835.640000001</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>26103604.89</v>
+        <v>8578898.789999999</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>27157540.91</v>
+        <v>11448686.65</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>27157274.58</v>
+        <v>11482975.88</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>27647572.73</v>
+        <v>9720394.306</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>28071616.88</v>
+        <v>11239511.93</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>28673886.48</v>
+        <v>10962776.61</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>29251594.07</v>
+        <v>11604476.28</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>30336273.72</v>
+        <v>12210785.55</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>30618300.22</v>
+        <v>10392528.57</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>33892947.46</v>
+        <v>12296567.31</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>34241672.7</v>
+        <v>10611347.57</v>
       </c>
       <c r="P8" s="10" t="n">
-        <v>37257937.51000001</v>
+        <v>11956035.3</v>
       </c>
       <c r="Q8" s="10" t="n">
-        <v>35108314.21</v>
+        <v>13774906.51</v>
       </c>
       <c r="R8" s="10" t="n">
-        <v>37298703.84</v>
+        <v>14311708.45</v>
       </c>
       <c r="S8" s="10" t="n">
-        <v>37783409</v>
+        <v>15107825.25</v>
       </c>
       <c r="T8" s="10" t="n">
-        <v>38089968.8</v>
+        <v>15073778.41</v>
       </c>
       <c r="U8" s="10" t="n">
-        <v>37204282.24</v>
+        <v>14418592.17</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>35935030.43</v>
+        <v>14254171.786</v>
       </c>
       <c r="W8" s="10" t="n">
-        <v>33047776.53057453</v>
+        <v>12876882.05</v>
       </c>
       <c r="X8" s="10" t="n">
-        <v>32306582.3</v>
+        <v>14611496.09</v>
       </c>
       <c r="Y8" s="10" t="n">
-        <v>31935257</v>
+        <v>12166751.06</v>
       </c>
       <c r="Z8" s="10" t="n">
-        <v>32498582.79</v>
+        <v>16621576.62</v>
       </c>
       <c r="AA8" s="10" t="n">
-        <v>35228696.4</v>
+        <v>14514309.01576271</v>
       </c>
       <c r="AB8" s="10" t="n">
-        <v>35459652.27</v>
+        <v>14531796.8503</v>
       </c>
       <c r="AC8" s="10" t="n">
-        <v>36336257.99</v>
+        <v>17101692.03703327</v>
       </c>
       <c r="AD8" s="10" t="n">
-        <v>35994272</v>
+        <v>14931033.79</v>
       </c>
       <c r="AE8" s="10" t="n">
-        <v>35659699.07</v>
+        <v>16808491.76</v>
       </c>
       <c r="AF8" s="10" t="n">
-        <v>34931731.8</v>
+        <v>16843990.58</v>
       </c>
       <c r="AG8" s="10" t="n">
-        <v>36921956.74</v>
+        <v>21912897.99750356</v>
       </c>
       <c r="AH8" s="10" t="n">
-        <v>36846894.38</v>
+        <v>19061337.28443</v>
       </c>
       <c r="AI8" s="10" t="n">
-        <v>36997106.92</v>
+        <v>21717989.15</v>
       </c>
       <c r="AJ8" s="10" t="n">
-        <v>36638380.34</v>
+        <v>21221983.031</v>
       </c>
       <c r="AK8" s="10" t="n">
-        <v>36795385.45</v>
+        <v>19401999.32</v>
       </c>
       <c r="AL8" s="10" t="n">
-        <v>36912992.83</v>
+        <v>20302133.71</v>
       </c>
       <c r="AM8" s="10" t="n">
-        <v>39683266.91</v>
+        <v>19376025.52</v>
       </c>
       <c r="AN8" s="10" t="n">
-        <v>40525687.26</v>
+        <v>20068914.47</v>
       </c>
       <c r="AO8" s="10" t="n">
-        <v>40674018.16</v>
+        <v>22682071.0394</v>
       </c>
       <c r="AP8" s="10" t="n">
-        <v>40981095.29</v>
+        <v>20373300.64776801</v>
       </c>
       <c r="AQ8" s="10" t="n">
-        <v>40540904.94</v>
+        <v>19367394.8239</v>
       </c>
       <c r="AR8" s="10" t="n">
-        <v>41742556.37333333</v>
+        <v>18011637.16812</v>
       </c>
       <c r="AS8" s="10" t="n">
-        <v>41750262.2</v>
+        <v>20063869.77305</v>
       </c>
       <c r="AT8" s="10" t="n">
-        <v>40971042.16</v>
+        <v>18945057.16586</v>
       </c>
       <c r="AU8" s="10" t="n">
-        <v>40782449.38</v>
+        <v>21338655.664084</v>
       </c>
       <c r="AV8" s="10" t="n">
-        <v>40721008</v>
+        <v>21431476.52</v>
       </c>
       <c r="AW8" s="10" t="n">
-        <v>40704930</v>
+        <v>21198056.54</v>
       </c>
       <c r="AX8" s="10" t="n">
-        <v>40527418</v>
+        <v>23400701.64</v>
       </c>
       <c r="AY8" s="10" t="n">
-        <v>42712345</v>
+        <v>19755778.5</v>
       </c>
       <c r="AZ8" s="10" t="n">
-        <v>43231443.56</v>
+        <v>20926547.08</v>
       </c>
       <c r="BA8" s="10" t="n">
-        <v>44297382</v>
+        <v>22438247.56</v>
       </c>
       <c r="BB8" s="10" t="n">
-        <v>44883310</v>
+        <v>23520051.4</v>
       </c>
       <c r="BC8" s="10" t="n">
-        <v>45046382</v>
+        <v>23108741.32</v>
       </c>
       <c r="BD8" s="10" t="n">
-        <v>49866100</v>
+        <v>24842686.74</v>
       </c>
       <c r="BE8" s="10" t="n">
-        <v>43404400.922647</v>
+        <v>31015231.63</v>
       </c>
       <c r="BF8" s="10" t="n">
-        <v>41671421.14</v>
+        <v>37452085.42</v>
       </c>
       <c r="BG8" s="10" t="n">
-        <v>40330077</v>
+        <v>40054821.34915254</v>
       </c>
       <c r="BH8" s="10" t="n">
-        <v>39711561</v>
+        <v>37864126</v>
       </c>
       <c r="BI8" s="10" t="n">
-        <v>39601317.5</v>
+        <v>39769304</v>
       </c>
       <c r="BJ8" s="10" t="n">
-        <v>39122907.65343537</v>
+        <v>38179519</v>
       </c>
       <c r="BK8" s="10" t="n">
-        <v>40085854</v>
+        <v>31309508</v>
       </c>
       <c r="BL8" s="10" t="n">
-        <v>40148865.7301075</v>
+        <v>39291548.26695399</v>
       </c>
       <c r="BM8" s="10" t="n">
-        <v>40428860.01733332</v>
+        <v>29792746.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>EBITDA</t>
+          <t>Gross Profit</t>
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>-4678332.310000002</v>
+        <v>27674794.07</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>-11074676.94101695</v>
+        <v>14079792.69898305</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>-12389363.7865</v>
+        <v>14707620.8335</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>-12750622.68</v>
+        <v>13352982.21</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>-9492325.0865</v>
+        <v>17665215.8235</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>-9273318.792730775</v>
+        <v>17883955.78726923</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>-125697.7131186016</v>
+        <v>27521875.0168814</v>
       </c>
       <c r="I9" s="10" t="n">
-        <v>-12142970.38440675</v>
+        <v>15928646.49559324</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>-11109908.97249999</v>
+        <v>17563977.50750002</v>
       </c>
       <c r="K9" s="10" t="n">
-        <v>-12581919.35</v>
+        <v>16669674.72</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>-11490534.177</v>
+        <v>18845739.543</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>-11944733.54</v>
+        <v>18673566.68</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>1941396.141302414</v>
+        <v>35834343.60130242</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>-17135281.9861017</v>
+        <v>17106390.7138983</v>
       </c>
       <c r="P9" s="10" t="n">
-        <v>-21994798.57897458</v>
+        <v>15263138.93102542</v>
       </c>
       <c r="Q9" s="10" t="n">
-        <v>-17471587.84176087</v>
+        <v>17636726.36823913</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>-17008951.7155</v>
+        <v>20289752.1245</v>
       </c>
       <c r="S9" s="10" t="n">
-        <v>-20395137.71618644</v>
+        <v>17388271.28381356</v>
       </c>
       <c r="T9" s="10" t="n">
-        <v>-15406582.91000001</v>
+        <v>22683385.89</v>
       </c>
       <c r="U9" s="10" t="n">
-        <v>-14800624.01000001</v>
+        <v>22403658.23</v>
       </c>
       <c r="V9" s="10" t="n">
-        <v>-12909770.596</v>
+        <v>23025259.834</v>
       </c>
       <c r="W9" s="10" t="n">
-        <v>-4582858.500574525</v>
+        <v>28464918.03</v>
       </c>
       <c r="X9" s="10" t="n">
-        <v>-3396105.629999999</v>
+        <v>28910476.67</v>
       </c>
       <c r="Y9" s="10" t="n">
-        <v>-2779207.109999996</v>
+        <v>29156049.89</v>
       </c>
       <c r="Z9" s="10" t="n">
-        <v>238914.7899999917</v>
+        <v>32737497.57999999</v>
       </c>
       <c r="AA9" s="10" t="n">
-        <v>-4616468.54576271</v>
+        <v>30612227.85423729</v>
       </c>
       <c r="AB9" s="10" t="n">
-        <v>-8218302.300360575</v>
+        <v>27241349.96963943</v>
       </c>
       <c r="AC9" s="10" t="n">
-        <v>-3405267.791033268</v>
+        <v>32930990.19896673</v>
       </c>
       <c r="AD9" s="10" t="n">
-        <v>-2559835.789999999</v>
+        <v>33434436.21</v>
       </c>
       <c r="AE9" s="10" t="n">
-        <v>-949900.0047999993</v>
+        <v>34709799.0652</v>
       </c>
       <c r="AF9" s="10" t="n">
-        <v>662250.3624000028</v>
+        <v>35593982.1624</v>
       </c>
       <c r="AG9" s="10" t="n">
-        <v>-2203267.225699753</v>
+        <v>34718689.51430025</v>
       </c>
       <c r="AH9" s="10" t="n">
-        <v>3099416.875705607</v>
+        <v>39946311.25570561</v>
       </c>
       <c r="AI9" s="10" t="n">
-        <v>7546577.93</v>
+        <v>44543684.85</v>
       </c>
       <c r="AJ9" s="10" t="n">
-        <v>8115056.629000001</v>
+        <v>44753436.969</v>
       </c>
       <c r="AK9" s="10" t="n">
-        <v>7041420.229999997</v>
+        <v>43836805.68</v>
       </c>
       <c r="AL9" s="10" t="n">
-        <v>10229269.08750001</v>
+        <v>47142261.9175</v>
       </c>
       <c r="AM9" s="10" t="n">
-        <v>3722356.078228258</v>
+        <v>43405622.98822826</v>
       </c>
       <c r="AN9" s="10" t="n">
-        <v>319829.776341863</v>
+        <v>40845517.03634186</v>
       </c>
       <c r="AO9" s="10" t="n">
-        <v>1730570.491375312</v>
+        <v>42404588.65137531</v>
       </c>
       <c r="AP9" s="10" t="n">
-        <v>2189295.821730457</v>
+        <v>43170391.11173046</v>
       </c>
       <c r="AQ9" s="10" t="n">
-        <v>2618.498726502061</v>
+        <v>40543523.4387265</v>
       </c>
       <c r="AR9" s="10" t="n">
-        <v>121926.1168958694</v>
+        <v>41864482.4902292</v>
       </c>
       <c r="AS9" s="10" t="n">
-        <v>612120.96435</v>
+        <v>42362383.16435</v>
       </c>
       <c r="AT9" s="10" t="n">
-        <v>549185.3818784654</v>
+        <v>41520227.54187846</v>
       </c>
       <c r="AU9" s="10" t="n">
-        <v>1106481.955915995</v>
+        <v>41888931.335916</v>
       </c>
       <c r="AV9" s="10" t="n">
-        <v>712592.9730889052</v>
+        <v>41433600.97308891</v>
       </c>
       <c r="AW9" s="10" t="n">
-        <v>1460327.926616006</v>
+        <v>42165257.92661601</v>
       </c>
       <c r="AX9" s="10" t="n">
-        <v>4152929.68243356</v>
+        <v>44680347.68243356</v>
       </c>
       <c r="AY9" s="10" t="n">
-        <v>664597.7241476029</v>
+        <v>43376942.7241476</v>
       </c>
       <c r="AZ9" s="10" t="n">
-        <v>436139.3247267008</v>
+        <v>43667582.8847267</v>
       </c>
       <c r="BA9" s="10" t="n">
-        <v>522683.8428319991</v>
+        <v>44820065.842832</v>
       </c>
       <c r="BB9" s="10" t="n">
-        <v>626705.9606759921</v>
+        <v>45510015.96067599</v>
       </c>
       <c r="BC9" s="10" t="n">
-        <v>-1363783.066139005</v>
+        <v>43682598.93386099</v>
       </c>
       <c r="BD9" s="10" t="n">
-        <v>-6168734.191525146</v>
+        <v>43697365.80847485</v>
       </c>
       <c r="BE9" s="10" t="n">
-        <v>-1052198.552647002</v>
+        <v>42352202.37</v>
       </c>
       <c r="BF9" s="10" t="n">
-        <v>782609.538036108</v>
+        <v>42454030.67803611</v>
       </c>
       <c r="BG9" s="10" t="n">
-        <v>1883014.152372979</v>
+        <v>42213091.15237298</v>
       </c>
       <c r="BH9" s="10" t="n">
-        <v>1335277.7629897</v>
+        <v>41046838.7629897</v>
       </c>
       <c r="BI9" s="10" t="n">
-        <v>1789651.063948035</v>
+        <v>41390968.56394804</v>
       </c>
       <c r="BJ9" s="10" t="n">
-        <v>2329994.141015492</v>
+        <v>41452901.79445086</v>
       </c>
       <c r="BK9" s="10" t="n">
-        <v>1128331.460800007</v>
+        <v>41214185.46080001</v>
       </c>
       <c r="BL9" s="10" t="n">
-        <v>4263496.534872413</v>
+        <v>44412362.26497991</v>
       </c>
       <c r="BM9" s="10" t="n">
-        <v>5030510.517666675</v>
+        <v>45459370.535</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Net Profit</t>
+          <t>Indirect Expenses</t>
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>-22852918.39160501</v>
+        <v>32353126.38</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>-11225765.79101695</v>
+        <v>25154469.64</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>-12706458.3365</v>
+        <v>27096984.62</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>-20614573.16</v>
+        <v>26103604.89</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>-10978378.2065</v>
+        <v>27157540.91</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>-10595631.79273077</v>
+        <v>27157274.58</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>-2978689.713118602</v>
+        <v>27647572.73</v>
       </c>
       <c r="I10" s="10" t="n">
-        <v>-19693663.76440675</v>
+        <v>28071616.88</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>-19468459.40249998</v>
+        <v>28673886.48</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>-19279999.38</v>
+        <v>29251594.07</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>-21007798.977</v>
+        <v>30336273.72</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>-18328525.22</v>
+        <v>30618300.22</v>
       </c>
       <c r="N10" s="10" t="n">
-        <v>-4902464.858697586</v>
+        <v>33892947.46</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>-17727620.2861017</v>
+        <v>34241672.7</v>
       </c>
       <c r="P10" s="10" t="n">
-        <v>-29847884.59897458</v>
+        <v>37257937.51000001</v>
       </c>
       <c r="Q10" s="10" t="n">
-        <v>-20031310.86176087</v>
+        <v>35108314.21</v>
       </c>
       <c r="R10" s="10" t="n">
-        <v>-21012400.9155</v>
+        <v>37298703.84</v>
       </c>
       <c r="S10" s="10" t="n">
-        <v>-29503943.31618644</v>
+        <v>37783409</v>
       </c>
       <c r="T10" s="10" t="n">
-        <v>-22864634.25000001</v>
+        <v>38089968.8</v>
       </c>
       <c r="U10" s="10" t="n">
-        <v>-21126250.36000001</v>
+        <v>37204282.24</v>
       </c>
       <c r="V10" s="10" t="n">
-        <v>-13574227.066</v>
+        <v>35935030.43</v>
       </c>
       <c r="W10" s="10" t="n">
-        <v>-3882962.040574525</v>
+        <v>33047776.53057453</v>
       </c>
       <c r="X10" s="10" t="n">
-        <v>-3641115.999999999</v>
+        <v>32306582.3</v>
       </c>
       <c r="Y10" s="10" t="n">
-        <v>-3800927.219999996</v>
+        <v>31935257</v>
       </c>
       <c r="Z10" s="10" t="n">
-        <v>-505602.9500000083</v>
+        <v>32498582.79</v>
       </c>
       <c r="AA10" s="10" t="n">
-        <v>-5392517.73576271</v>
+        <v>35228696.4</v>
       </c>
       <c r="AB10" s="10" t="n">
-        <v>-9524492.300360575</v>
+        <v>35459652.27</v>
       </c>
       <c r="AC10" s="10" t="n">
-        <v>-7762203.881033268</v>
+        <v>36336257.99</v>
       </c>
       <c r="AD10" s="10" t="n">
-        <v>-6393200.879999999</v>
+        <v>35994272</v>
       </c>
       <c r="AE10" s="10" t="n">
-        <v>-4506470.134799999</v>
+        <v>35659699.07</v>
       </c>
       <c r="AF10" s="10" t="n">
-        <v>-5040129.987599997</v>
+        <v>34931731.8</v>
       </c>
       <c r="AG10" s="10" t="n">
-        <v>-5010081.635699753</v>
+        <v>36921956.74</v>
       </c>
       <c r="AH10" s="10" t="n">
-        <v>-2244857.254294393</v>
+        <v>36846894.38</v>
       </c>
       <c r="AI10" s="10" t="n">
-        <v>-3218378.410000001</v>
+        <v>36997106.92</v>
       </c>
       <c r="AJ10" s="10" t="n">
-        <v>-2931234.210999998</v>
+        <v>36638380.34</v>
       </c>
       <c r="AK10" s="10" t="n">
-        <v>1240414.029999997</v>
+        <v>36795385.45</v>
       </c>
       <c r="AL10" s="10" t="n">
-        <v>-14823109.43249999</v>
+        <v>36912992.83</v>
       </c>
       <c r="AM10" s="10" t="n">
-        <v>931511.3782282574</v>
+        <v>39683266.91</v>
       </c>
       <c r="AN10" s="10" t="n">
-        <v>-474241.8036581371</v>
+        <v>40525687.26</v>
       </c>
       <c r="AO10" s="10" t="n">
-        <v>1051592.291375312</v>
+        <v>40674018.16</v>
       </c>
       <c r="AP10" s="10" t="n">
-        <v>148686.4817304574</v>
+        <v>40981095.29</v>
       </c>
       <c r="AQ10" s="10" t="n">
-        <v>-619704.1212734979</v>
+        <v>40540904.94</v>
       </c>
       <c r="AR10" s="10" t="n">
-        <v>-977762.2931041308</v>
+        <v>41742556.37333333</v>
       </c>
       <c r="AS10" s="10" t="n">
-        <v>-2316962.23565</v>
+        <v>41750262.2</v>
       </c>
       <c r="AT10" s="10" t="n">
-        <v>-8191020.758121535</v>
+        <v>40971042.16</v>
       </c>
       <c r="AU10" s="10" t="n">
-        <v>-6921865.504084005</v>
+        <v>40782449.38</v>
       </c>
       <c r="AV10" s="10" t="n">
-        <v>145165.9730889052</v>
+        <v>40721008</v>
       </c>
       <c r="AW10" s="10" t="n">
-        <v>182749.9266160056</v>
+        <v>40704930</v>
       </c>
       <c r="AX10" s="10" t="n">
-        <v>-7877311.31756644</v>
+        <v>40527418</v>
       </c>
       <c r="AY10" s="10" t="n">
-        <v>359675.7241476029</v>
+        <v>42712345</v>
       </c>
       <c r="AZ10" s="10" t="n">
-        <v>137720.3247267008</v>
+        <v>43231443.56</v>
       </c>
       <c r="BA10" s="10" t="n">
-        <v>157628.8428319991</v>
+        <v>44297382</v>
       </c>
       <c r="BB10" s="10" t="n">
-        <v>105283.9606759921</v>
+        <v>44883310</v>
       </c>
       <c r="BC10" s="10" t="n">
-        <v>-1716808.066139005</v>
+        <v>45046382</v>
       </c>
       <c r="BD10" s="10" t="n">
-        <v>-8018981.191525146</v>
+        <v>49866100</v>
       </c>
       <c r="BE10" s="10" t="n">
-        <v>-3861594.552647002</v>
+        <v>43404400.922647</v>
       </c>
       <c r="BF10" s="10" t="n">
-        <v>-304562.461963892</v>
+        <v>41671421.14</v>
       </c>
       <c r="BG10" s="10" t="n">
-        <v>884007.1523729786</v>
+        <v>40330077</v>
       </c>
       <c r="BH10" s="10" t="n">
-        <v>122781.7629896998</v>
+        <v>39711561</v>
       </c>
       <c r="BI10" s="10" t="n">
-        <v>167795.0639480352</v>
+        <v>39601317.5</v>
       </c>
       <c r="BJ10" s="10" t="n">
-        <v>-22730063.85898451</v>
+        <v>39122907.65343537</v>
       </c>
       <c r="BK10" s="10" t="n">
-        <v>138321.460800007</v>
+        <v>40085854</v>
       </c>
       <c r="BL10" s="10" t="n">
-        <v>3349094.534872413</v>
+        <v>40148865.7301075</v>
       </c>
       <c r="BM10" s="10" t="n">
-        <v>4101588.517666675</v>
+        <v>40428860.01733332</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>-4678332.310000002</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>-11074676.94101695</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>-12389363.7865</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>-12750622.68</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>-9492325.0865</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>-9273318.792730775</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>-125697.7131186016</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>-12142970.38440675</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>-11109908.97249999</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>-12581919.35</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>-11490534.177</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>-11944733.54</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>1941396.141302414</v>
+      </c>
+      <c r="O11" s="10" t="n">
+        <v>-17135281.9861017</v>
+      </c>
+      <c r="P11" s="10" t="n">
+        <v>-21994798.57897458</v>
+      </c>
+      <c r="Q11" s="10" t="n">
+        <v>-17471587.84176087</v>
+      </c>
+      <c r="R11" s="10" t="n">
+        <v>-17008951.7155</v>
+      </c>
+      <c r="S11" s="10" t="n">
+        <v>-20395137.71618644</v>
+      </c>
+      <c r="T11" s="10" t="n">
+        <v>-15406582.91000001</v>
+      </c>
+      <c r="U11" s="10" t="n">
+        <v>-14800624.01000001</v>
+      </c>
+      <c r="V11" s="10" t="n">
+        <v>-12909770.596</v>
+      </c>
+      <c r="W11" s="10" t="n">
+        <v>-4582858.500574525</v>
+      </c>
+      <c r="X11" s="10" t="n">
+        <v>-3396105.629999999</v>
+      </c>
+      <c r="Y11" s="10" t="n">
+        <v>-2779207.109999996</v>
+      </c>
+      <c r="Z11" s="10" t="n">
+        <v>238914.7899999917</v>
+      </c>
+      <c r="AA11" s="10" t="n">
+        <v>-4616468.54576271</v>
+      </c>
+      <c r="AB11" s="10" t="n">
+        <v>-8218302.300360575</v>
+      </c>
+      <c r="AC11" s="10" t="n">
+        <v>-3405267.791033268</v>
+      </c>
+      <c r="AD11" s="10" t="n">
+        <v>-2559835.789999999</v>
+      </c>
+      <c r="AE11" s="10" t="n">
+        <v>-949900.0047999993</v>
+      </c>
+      <c r="AF11" s="10" t="n">
+        <v>662250.3624000028</v>
+      </c>
+      <c r="AG11" s="10" t="n">
+        <v>-2203267.225699753</v>
+      </c>
+      <c r="AH11" s="10" t="n">
+        <v>3099416.875705607</v>
+      </c>
+      <c r="AI11" s="10" t="n">
+        <v>7546577.93</v>
+      </c>
+      <c r="AJ11" s="10" t="n">
+        <v>8115056.629000001</v>
+      </c>
+      <c r="AK11" s="10" t="n">
+        <v>7041420.229999997</v>
+      </c>
+      <c r="AL11" s="10" t="n">
+        <v>10229269.08750001</v>
+      </c>
+      <c r="AM11" s="10" t="n">
+        <v>3722356.078228258</v>
+      </c>
+      <c r="AN11" s="10" t="n">
+        <v>319829.776341863</v>
+      </c>
+      <c r="AO11" s="10" t="n">
+        <v>1730570.491375312</v>
+      </c>
+      <c r="AP11" s="10" t="n">
+        <v>2189295.821730457</v>
+      </c>
+      <c r="AQ11" s="10" t="n">
+        <v>2618.498726502061</v>
+      </c>
+      <c r="AR11" s="10" t="n">
+        <v>121926.1168958694</v>
+      </c>
+      <c r="AS11" s="10" t="n">
+        <v>612120.96435</v>
+      </c>
+      <c r="AT11" s="10" t="n">
+        <v>549185.3818784654</v>
+      </c>
+      <c r="AU11" s="10" t="n">
+        <v>1106481.955915995</v>
+      </c>
+      <c r="AV11" s="10" t="n">
+        <v>712592.9730889052</v>
+      </c>
+      <c r="AW11" s="10" t="n">
+        <v>1460327.926616006</v>
+      </c>
+      <c r="AX11" s="10" t="n">
+        <v>4152929.68243356</v>
+      </c>
+      <c r="AY11" s="10" t="n">
+        <v>664597.7241476029</v>
+      </c>
+      <c r="AZ11" s="10" t="n">
+        <v>436139.3247267008</v>
+      </c>
+      <c r="BA11" s="10" t="n">
+        <v>522683.8428319991</v>
+      </c>
+      <c r="BB11" s="10" t="n">
+        <v>626705.9606759921</v>
+      </c>
+      <c r="BC11" s="10" t="n">
+        <v>-1363783.066139005</v>
+      </c>
+      <c r="BD11" s="10" t="n">
+        <v>-6168734.191525146</v>
+      </c>
+      <c r="BE11" s="10" t="n">
+        <v>-1052198.552647002</v>
+      </c>
+      <c r="BF11" s="10" t="n">
+        <v>782609.538036108</v>
+      </c>
+      <c r="BG11" s="10" t="n">
+        <v>1883014.152372979</v>
+      </c>
+      <c r="BH11" s="10" t="n">
+        <v>1335277.7629897</v>
+      </c>
+      <c r="BI11" s="10" t="n">
+        <v>1789651.063948035</v>
+      </c>
+      <c r="BJ11" s="10" t="n">
+        <v>2329994.141015492</v>
+      </c>
+      <c r="BK11" s="10" t="n">
+        <v>1128331.460800007</v>
+      </c>
+      <c r="BL11" s="10" t="n">
+        <v>4263496.534872413</v>
+      </c>
+      <c r="BM11" s="10" t="n">
+        <v>5030510.517666675</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Net Profit</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>-22852918.39160501</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>-11225765.79101695</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>-12706458.3365</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>-20614573.16</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>-10978378.2065</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>-10595631.79273077</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>-2978689.713118602</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>-19693663.76440675</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>-19468459.40249998</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>-19279999.38</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>-21007798.977</v>
+      </c>
+      <c r="M12" s="10" t="n">
+        <v>-18328525.22</v>
+      </c>
+      <c r="N12" s="10" t="n">
+        <v>-4902464.858697586</v>
+      </c>
+      <c r="O12" s="10" t="n">
+        <v>-17727620.2861017</v>
+      </c>
+      <c r="P12" s="10" t="n">
+        <v>-29847884.59897458</v>
+      </c>
+      <c r="Q12" s="10" t="n">
+        <v>-20031310.86176087</v>
+      </c>
+      <c r="R12" s="10" t="n">
+        <v>-21012400.9155</v>
+      </c>
+      <c r="S12" s="10" t="n">
+        <v>-29503943.31618644</v>
+      </c>
+      <c r="T12" s="10" t="n">
+        <v>-22864634.25000001</v>
+      </c>
+      <c r="U12" s="10" t="n">
+        <v>-21126250.36000001</v>
+      </c>
+      <c r="V12" s="10" t="n">
+        <v>-13574227.066</v>
+      </c>
+      <c r="W12" s="10" t="n">
+        <v>-3882962.040574525</v>
+      </c>
+      <c r="X12" s="10" t="n">
+        <v>-3641115.999999999</v>
+      </c>
+      <c r="Y12" s="10" t="n">
+        <v>-3800927.219999996</v>
+      </c>
+      <c r="Z12" s="10" t="n">
+        <v>-505602.9500000083</v>
+      </c>
+      <c r="AA12" s="10" t="n">
+        <v>-5392517.73576271</v>
+      </c>
+      <c r="AB12" s="10" t="n">
+        <v>-9524492.300360575</v>
+      </c>
+      <c r="AC12" s="10" t="n">
+        <v>-7762203.881033268</v>
+      </c>
+      <c r="AD12" s="10" t="n">
+        <v>-6393200.879999999</v>
+      </c>
+      <c r="AE12" s="10" t="n">
+        <v>-4506470.134799999</v>
+      </c>
+      <c r="AF12" s="10" t="n">
+        <v>-5040129.987599997</v>
+      </c>
+      <c r="AG12" s="10" t="n">
+        <v>-5010081.635699753</v>
+      </c>
+      <c r="AH12" s="10" t="n">
+        <v>-2244857.254294393</v>
+      </c>
+      <c r="AI12" s="10" t="n">
+        <v>-3218378.410000001</v>
+      </c>
+      <c r="AJ12" s="10" t="n">
+        <v>-2931234.210999998</v>
+      </c>
+      <c r="AK12" s="10" t="n">
+        <v>1240414.029999997</v>
+      </c>
+      <c r="AL12" s="10" t="n">
+        <v>-14823109.43249999</v>
+      </c>
+      <c r="AM12" s="10" t="n">
+        <v>931511.3782282574</v>
+      </c>
+      <c r="AN12" s="10" t="n">
+        <v>-474241.8036581371</v>
+      </c>
+      <c r="AO12" s="10" t="n">
+        <v>1051592.291375312</v>
+      </c>
+      <c r="AP12" s="10" t="n">
+        <v>148686.4817304574</v>
+      </c>
+      <c r="AQ12" s="10" t="n">
+        <v>-619704.1212734979</v>
+      </c>
+      <c r="AR12" s="10" t="n">
+        <v>-977762.2931041308</v>
+      </c>
+      <c r="AS12" s="10" t="n">
+        <v>-2316962.23565</v>
+      </c>
+      <c r="AT12" s="10" t="n">
+        <v>-8191020.758121535</v>
+      </c>
+      <c r="AU12" s="10" t="n">
+        <v>-6921865.504084005</v>
+      </c>
+      <c r="AV12" s="10" t="n">
+        <v>145165.9730889052</v>
+      </c>
+      <c r="AW12" s="10" t="n">
+        <v>182749.9266160056</v>
+      </c>
+      <c r="AX12" s="10" t="n">
+        <v>-7877311.31756644</v>
+      </c>
+      <c r="AY12" s="10" t="n">
+        <v>359675.7241476029</v>
+      </c>
+      <c r="AZ12" s="10" t="n">
+        <v>137720.3247267008</v>
+      </c>
+      <c r="BA12" s="10" t="n">
+        <v>157628.8428319991</v>
+      </c>
+      <c r="BB12" s="10" t="n">
+        <v>105283.9606759921</v>
+      </c>
+      <c r="BC12" s="10" t="n">
+        <v>-1716808.066139005</v>
+      </c>
+      <c r="BD12" s="10" t="n">
+        <v>-8018981.191525146</v>
+      </c>
+      <c r="BE12" s="10" t="n">
+        <v>-3861594.552647002</v>
+      </c>
+      <c r="BF12" s="10" t="n">
+        <v>-304562.461963892</v>
+      </c>
+      <c r="BG12" s="10" t="n">
+        <v>884007.1523729786</v>
+      </c>
+      <c r="BH12" s="10" t="n">
+        <v>122781.7629896998</v>
+      </c>
+      <c r="BI12" s="10" t="n">
+        <v>167795.0639480352</v>
+      </c>
+      <c r="BJ12" s="10" t="n">
+        <v>-22730063.85898451</v>
+      </c>
+      <c r="BK12" s="10" t="n">
+        <v>138321.460800007</v>
+      </c>
+      <c r="BL12" s="10" t="n">
+        <v>3349094.534872413</v>
+      </c>
+      <c r="BM12" s="10" t="n">
+        <v>4101588.517666675</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
           <t>Headcount</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B13" s="8" t="n">
         <v>246</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C13" s="8" t="n">
         <v>249</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D13" s="8" t="n">
         <v>250</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E13" s="8" t="n">
         <v>244</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F13" s="8" t="n">
         <v>238</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G13" s="8" t="n">
         <v>240</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H13" s="8" t="n">
         <v>244</v>
       </c>
-      <c r="I11" s="8" t="n">
+      <c r="I13" s="8" t="n">
         <v>246</v>
       </c>
-      <c r="J11" s="8" t="n">
+      <c r="J13" s="8" t="n">
         <v>248</v>
       </c>
-      <c r="K11" s="8" t="n">
+      <c r="K13" s="8" t="n">
         <v>262</v>
       </c>
-      <c r="L11" s="8" t="n">
+      <c r="L13" s="8" t="n">
         <v>267</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M13" s="8" t="n">
         <v>271</v>
       </c>
-      <c r="N11" s="8" t="n">
+      <c r="N13" s="8" t="n">
         <v>287</v>
       </c>
-      <c r="O11" s="8" t="n"/>
-      <c r="P11" s="8" t="n"/>
-      <c r="Q11" s="8" t="n"/>
-      <c r="R11" s="8" t="n"/>
-      <c r="S11" s="8" t="n"/>
-      <c r="T11" s="8" t="n"/>
-      <c r="U11" s="8" t="n"/>
-      <c r="V11" s="8" t="n"/>
-      <c r="W11" s="8" t="n"/>
-      <c r="X11" s="8" t="n"/>
-      <c r="Y11" s="8" t="n"/>
-      <c r="Z11" s="8" t="n"/>
-      <c r="AA11" s="8" t="n">
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="8" t="n"/>
+      <c r="T13" s="8" t="n"/>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="8" t="n"/>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="8" t="n"/>
+      <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n">
         <v>265</v>
       </c>
-      <c r="AB11" s="8" t="n">
+      <c r="AB13" s="8" t="n">
         <v>266</v>
       </c>
-      <c r="AC11" s="8" t="n">
+      <c r="AC13" s="8" t="n">
         <v>269</v>
       </c>
-      <c r="AD11" s="8" t="n">
+      <c r="AD13" s="8" t="n">
         <v>275</v>
       </c>
-      <c r="AE11" s="8" t="n">
+      <c r="AE13" s="8" t="n">
         <v>278</v>
       </c>
-      <c r="AF11" s="8" t="n">
+      <c r="AF13" s="8" t="n">
         <v>275</v>
       </c>
-      <c r="AG11" s="8" t="n">
+      <c r="AG13" s="8" t="n">
         <v>277</v>
       </c>
-      <c r="AH11" s="8" t="n">
+      <c r="AH13" s="8" t="n">
         <v>280</v>
       </c>
-      <c r="AI11" s="8" t="n">
+      <c r="AI13" s="8" t="n">
         <v>281</v>
       </c>
-      <c r="AJ11" s="8" t="n">
+      <c r="AJ13" s="8" t="n">
         <v>278</v>
       </c>
-      <c r="AK11" s="8" t="n">
+      <c r="AK13" s="8" t="n">
         <v>280</v>
       </c>
-      <c r="AL11" s="8" t="n">
+      <c r="AL13" s="8" t="n">
         <v>279</v>
       </c>
-      <c r="AM11" s="8" t="n">
+      <c r="AM13" s="8" t="n">
         <v>280</v>
       </c>
-      <c r="AN11" s="8" t="n">
+      <c r="AN13" s="8" t="n">
         <v>280</v>
       </c>
-      <c r="AO11" s="8" t="n">
+      <c r="AO13" s="8" t="n">
         <v>283</v>
       </c>
-      <c r="AP11" s="8" t="n">
+      <c r="AP13" s="8" t="n">
         <v>294</v>
       </c>
-      <c r="AQ11" s="8" t="n">
+      <c r="AQ13" s="8" t="n">
         <v>295</v>
       </c>
-      <c r="AR11" s="8" t="n">
+      <c r="AR13" s="8" t="n">
         <v>304</v>
       </c>
-      <c r="AS11" s="8" t="n">
+      <c r="AS13" s="8" t="n">
         <v>299</v>
       </c>
-      <c r="AT11" s="8" t="n">
+      <c r="AT13" s="8" t="n">
         <v>291</v>
       </c>
-      <c r="AU11" s="8" t="n">
+      <c r="AU13" s="8" t="n">
         <v>291</v>
       </c>
-      <c r="AV11" s="8" t="n">
+      <c r="AV13" s="8" t="n">
         <v>291</v>
       </c>
-      <c r="AW11" s="8" t="n">
+      <c r="AW13" s="8" t="n">
         <v>294</v>
       </c>
-      <c r="AX11" s="8" t="n">
+      <c r="AX13" s="8" t="n">
         <v>296</v>
       </c>
-      <c r="AY11" s="8" t="n">
+      <c r="AY13" s="8" t="n">
         <v>299</v>
       </c>
-      <c r="AZ11" s="8" t="n">
+      <c r="AZ13" s="8" t="n">
         <v>305</v>
       </c>
-      <c r="BA11" s="8" t="n">
+      <c r="BA13" s="8" t="n">
         <v>304</v>
       </c>
-      <c r="BB11" s="8" t="n">
+      <c r="BB13" s="8" t="n">
         <v>311</v>
       </c>
-      <c r="BC11" s="8" t="n">
+      <c r="BC13" s="8" t="n">
         <v>315</v>
       </c>
-      <c r="BD11" s="8" t="n">
+      <c r="BD13" s="8" t="n">
         <v>308</v>
       </c>
-      <c r="BE11" s="8" t="n">
+      <c r="BE13" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="BF11" s="8" t="n">
+      <c r="BF13" s="8" t="n">
         <v>289</v>
       </c>
-      <c r="BG11" s="8" t="n">
+      <c r="BG13" s="8" t="n">
         <v>289</v>
       </c>
-      <c r="BH11" s="8" t="n">
+      <c r="BH13" s="8" t="n">
         <v>283</v>
       </c>
-      <c r="BI11" s="8" t="n">
+      <c r="BI13" s="8" t="n">
         <v>281</v>
       </c>
-      <c r="BJ11" s="8" t="n">
+      <c r="BJ13" s="8" t="n">
         <v>276</v>
       </c>
-      <c r="BK11" s="8" t="n">
+      <c r="BK13" s="8" t="n">
         <v>276</v>
       </c>
-      <c r="BL11" s="8" t="n">
+      <c r="BL13" s="8" t="n">
         <v>273</v>
       </c>
-      <c r="BM11" s="8" t="n">
+      <c r="BM13" s="8" t="n">
         <v>273</v>
       </c>
     </row>
